--- a/Releves_Qonto_2025.xlsx
+++ b/Releves_Qonto_2025.xlsx
@@ -21,6 +21,7 @@
     <sheet name="2025-10" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="2025-11" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="2025-12" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Affectation_PCG" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,9 +30,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -71,11 +71,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -803,7 +804,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45876</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -813,7 +814,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -826,7 +827,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45876</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -836,7 +837,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -849,7 +850,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45884</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -859,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -926,7 +927,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45906</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -936,7 +937,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -949,7 +950,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45907</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -959,7 +960,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -972,7 +973,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45907</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -982,7 +983,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -995,7 +996,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45908</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1005,7 +1006,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>622600</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1018,7 +1019,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45911</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1028,7 +1029,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1041,7 +1042,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45911</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1051,7 +1052,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>411000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1064,7 +1065,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45911</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1074,7 +1075,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1087,7 +1088,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45914</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1097,7 +1098,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1110,7 +1111,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45915</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1120,7 +1121,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1133,7 +1134,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45916</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1143,7 +1144,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1156,7 +1157,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45916</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1166,7 +1167,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>580000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1179,7 +1180,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45917</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,7 +1190,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>580000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1202,7 +1203,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45917</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1225,7 +1226,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45918</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1235,7 +1236,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1248,7 +1249,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45918</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1258,7 +1259,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1271,7 +1272,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45925</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1281,7 +1282,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1294,7 +1295,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45925</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1304,7 +1305,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1317,7 +1318,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45926</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1327,7 +1328,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1340,7 +1341,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45927</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1350,7 +1351,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,7 +1418,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45933</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1427,7 +1428,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1440,7 +1441,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45935</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1450,7 +1451,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1463,7 +1464,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45936</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1473,7 +1474,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1486,7 +1487,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45937</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1496,7 +1497,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1509,7 +1510,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45937</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,7 +1520,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1532,7 +1533,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45938</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1542,7 +1543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1555,7 +1556,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45940</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1565,7 +1566,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1578,7 +1579,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45941</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1588,7 +1589,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>580000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1601,7 +1602,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45945</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1611,7 +1612,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1624,7 +1625,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45948</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1634,7 +1635,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1647,7 +1648,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45951</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1657,7 +1658,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1670,7 +1671,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45952</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1680,7 +1681,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1693,7 +1694,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45958</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1703,7 +1704,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1716,7 +1717,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45959</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1726,7 +1727,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>580000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1739,7 +1740,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45961</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1749,7 +1750,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1762,7 +1763,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45961</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1772,7 +1773,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1839,7 +1840,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45965</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1849,7 +1850,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1862,7 +1863,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45968</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1872,7 +1873,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1885,7 +1886,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45968</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1895,7 +1896,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1908,7 +1909,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45969</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1918,7 +1919,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1931,7 +1932,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45972</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1941,7 +1942,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1954,7 +1955,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45972</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1964,7 +1965,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1977,7 +1978,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45972</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1987,7 +1988,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2000,7 +2001,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45972</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -2010,7 +2011,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2023,7 +2024,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45972</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -2033,7 +2034,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2046,7 +2047,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45974</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -2056,7 +2057,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2069,7 +2070,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45974</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -2079,7 +2080,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2092,7 +2093,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45974</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -2102,7 +2103,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2115,7 +2116,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45975</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2125,7 +2126,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2138,7 +2139,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45975</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2148,7 +2149,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2161,7 +2162,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45975</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2171,7 +2172,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2184,7 +2185,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45975</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2194,7 +2195,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2207,7 +2208,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45976</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2217,7 +2218,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2230,7 +2231,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45978</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -2240,7 +2241,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2253,7 +2254,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45979</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2263,7 +2264,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2276,7 +2277,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45980</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2286,7 +2287,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2299,7 +2300,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2309,7 +2310,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2322,7 +2323,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45982</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2332,7 +2333,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2345,7 +2346,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45982</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2355,7 +2356,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2368,7 +2369,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45983</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2378,7 +2379,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2391,7 +2392,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>45986</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,7 +2402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2414,7 +2415,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>45989</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2424,7 +2425,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2437,7 +2438,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>45990</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2447,7 +2448,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2514,7 +2515,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45993</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -2524,7 +2525,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>411000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2537,7 +2538,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45993</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -2547,7 +2548,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2560,7 +2561,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45994</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -2570,7 +2571,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2583,7 +2584,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45994</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -2593,7 +2594,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2606,7 +2607,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45994</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -2616,7 +2617,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2629,7 +2630,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45995</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -2639,7 +2640,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2652,7 +2653,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45995</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -2662,7 +2663,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2675,7 +2676,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45997</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -2685,7 +2686,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2698,7 +2699,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45998</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -2708,7 +2709,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2721,7 +2722,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45998</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -2731,7 +2732,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2744,7 +2745,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>46000</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -2754,7 +2755,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2767,7 +2768,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>46000</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -2777,7 +2778,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2790,7 +2791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>46002</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2800,7 +2801,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2813,7 +2814,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>46002</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2823,7 +2824,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2836,7 +2837,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>46003</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2846,7 +2847,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2859,7 +2860,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>46005</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2869,7 +2870,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2882,7 +2883,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>46005</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2892,7 +2893,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2905,7 +2906,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>46007</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -2915,7 +2916,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2928,7 +2929,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>46008</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2938,7 +2939,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2951,7 +2952,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>46008</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2961,7 +2962,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2974,7 +2975,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>46010</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2984,7 +2985,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2997,7 +2998,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>46020</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -3007,7 +3008,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3020,7 +3021,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>46020</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -3030,7 +3031,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>618500</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3043,7 +3044,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>46021</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -3053,7 +3054,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>455100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3066,7 +3067,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>46021</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -3076,7 +3077,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>455100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3089,7 +3090,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>46021</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -3099,7 +3100,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>455100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3109,6 +3110,267 @@
       </c>
       <c r="F27" s="2" t="n">
         <v>12000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valeur</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Occurrences</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>affranchissement</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>assurances</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cadeaux clientele</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>compte courant associe</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cotisations</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>formation</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>frais bancaires</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>honoraires</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>licences logiciels</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>petit equipement</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>receptions</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reglement client</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>tva a decaisser</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>virement interne</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Regle appliquee</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>voyages et deplacements</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3886,7 +4148,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45663</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -3896,7 +4158,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>580000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3909,7 +4171,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45664</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -3919,7 +4181,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3932,7 +4194,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45664</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -3942,7 +4204,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3955,7 +4217,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45669</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -3965,7 +4227,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3978,7 +4240,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45671</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -3988,7 +4250,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4001,7 +4263,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45671</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -4011,7 +4273,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4024,7 +4286,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45671</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -4034,7 +4296,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4047,7 +4309,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45672</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -4057,7 +4319,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4070,7 +4332,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45673</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -4080,7 +4342,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4093,7 +4355,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45674</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -4103,7 +4365,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4116,7 +4378,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45674</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -4126,7 +4388,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4139,7 +4401,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45674</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -4149,7 +4411,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4162,7 +4424,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45674</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -4172,7 +4434,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4185,7 +4447,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45675</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -4195,7 +4457,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4208,7 +4470,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45675</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -4218,7 +4480,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4231,7 +4493,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45675</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -4241,7 +4503,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4254,7 +4516,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45676</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -4264,7 +4526,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4277,7 +4539,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45678</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -4287,7 +4549,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4300,7 +4562,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45679</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -4310,7 +4572,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4323,7 +4585,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45680</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -4333,7 +4595,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4346,7 +4608,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45680</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -4356,7 +4618,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4369,7 +4631,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45680</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -4379,7 +4641,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4392,7 +4654,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45680</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -4402,7 +4664,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4415,7 +4677,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45680</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -4425,7 +4687,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4438,7 +4700,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>45681</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -4448,7 +4710,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4461,7 +4723,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>45682</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -4471,7 +4733,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4484,7 +4746,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>45684</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -4494,7 +4756,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4507,7 +4769,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>45684</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -4517,7 +4779,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4530,7 +4792,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>45685</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -4540,7 +4802,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4553,7 +4815,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>45686</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -4563,7 +4825,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4576,7 +4838,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>45687</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -4586,7 +4848,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4599,7 +4861,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="4" t="n">
         <v>45688</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -4609,7 +4871,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>445510</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4622,7 +4884,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="4" t="n">
         <v>45688</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -4632,7 +4894,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4645,7 +4907,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="4" t="n">
         <v>45688</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -4655,7 +4917,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4668,7 +4930,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="4" t="n">
         <v>45688</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -4678,7 +4940,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4745,7 +5007,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45689</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -4755,7 +5017,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4768,7 +5030,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45689</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -4778,7 +5040,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4791,7 +5053,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45689</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -4801,7 +5063,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4814,7 +5076,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45689</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -4824,7 +5086,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4837,7 +5099,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45690</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -4847,7 +5109,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4860,7 +5122,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45691</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -4870,7 +5132,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4883,7 +5145,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45691</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -4893,7 +5155,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4906,7 +5168,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45692</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -4916,7 +5178,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4929,7 +5191,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45692</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -4939,7 +5201,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4952,7 +5214,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45693</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -4962,7 +5224,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>616000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4975,7 +5237,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45693</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -4985,7 +5247,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4998,7 +5260,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45694</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -5008,7 +5270,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5021,7 +5283,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45694</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -5031,7 +5293,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5044,7 +5306,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45695</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -5054,7 +5316,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5067,7 +5329,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45695</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -5077,7 +5339,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5090,7 +5352,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45696</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -5100,7 +5362,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5113,7 +5375,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45696</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -5123,7 +5385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5136,7 +5398,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45696</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -5146,7 +5408,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5159,7 +5421,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45697</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -5169,7 +5431,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5182,7 +5444,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45697</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -5192,7 +5454,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5205,7 +5467,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45699</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -5215,7 +5477,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5228,7 +5490,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45699</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -5238,7 +5500,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5251,7 +5513,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45699</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -5261,7 +5523,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5274,7 +5536,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45700</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -5284,7 +5546,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5297,7 +5559,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>45701</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -5307,7 +5569,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>618500</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5320,7 +5582,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>45701</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -5330,7 +5592,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5343,7 +5605,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>45702</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -5353,7 +5615,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5366,7 +5628,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>45703</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -5376,7 +5638,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5389,7 +5651,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>45703</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -5399,7 +5661,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5412,7 +5674,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>45704</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -5422,7 +5684,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5435,7 +5697,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>45704</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -5445,7 +5707,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5458,7 +5720,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="4" t="n">
         <v>45704</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -5468,7 +5730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5481,7 +5743,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="4" t="n">
         <v>45706</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -5491,7 +5753,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5504,7 +5766,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="4" t="n">
         <v>45706</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -5514,7 +5776,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5527,7 +5789,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="4" t="n">
         <v>45707</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -5537,7 +5799,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5550,7 +5812,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="4" t="n">
         <v>45707</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -5560,7 +5822,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5573,7 +5835,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="4" t="n">
         <v>45709</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -5583,7 +5845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5596,7 +5858,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="4" t="n">
         <v>45710</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -5606,7 +5868,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>622600</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5619,7 +5881,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="4" t="n">
         <v>45712</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -5629,7 +5891,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5642,7 +5904,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="4" t="n">
         <v>45712</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -5652,7 +5914,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5665,7 +5927,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="4" t="n">
         <v>45712</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -5675,7 +5937,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5688,7 +5950,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="4" t="n">
         <v>45713</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -5698,7 +5960,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>622600</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5711,7 +5973,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="4" t="n">
         <v>45713</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -5721,7 +5983,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5788,7 +6050,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45717</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -5798,7 +6060,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5811,7 +6073,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45718</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -5821,7 +6083,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5834,7 +6096,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45719</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -5844,7 +6106,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5857,7 +6119,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45720</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -5867,7 +6129,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5880,7 +6142,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45720</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -5890,7 +6152,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5903,7 +6165,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45721</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -5913,7 +6175,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5926,7 +6188,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45721</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -5936,7 +6198,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5949,7 +6211,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45721</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -5959,7 +6221,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5972,7 +6234,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45722</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -5982,7 +6244,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>618500</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5995,7 +6257,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45722</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -6005,7 +6267,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6018,7 +6280,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45722</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -6028,7 +6290,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6041,7 +6303,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45723</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -6051,7 +6313,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>616000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6064,7 +6326,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45723</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -6074,7 +6336,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6087,7 +6349,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45723</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -6097,7 +6359,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6110,7 +6372,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45723</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -6120,7 +6382,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6133,7 +6395,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45723</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -6143,7 +6405,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6156,7 +6418,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45723</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -6166,7 +6428,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6179,7 +6441,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45724</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -6189,7 +6451,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6202,7 +6464,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45726</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -6212,7 +6474,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>623400</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6225,7 +6487,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45727</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -6235,7 +6497,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6248,7 +6510,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45727</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -6258,7 +6520,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6271,7 +6533,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45728</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -6281,7 +6543,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6294,7 +6556,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45728</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -6304,7 +6566,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6317,7 +6579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45728</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -6327,7 +6589,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6340,7 +6602,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>45729</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -6350,7 +6612,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6363,7 +6625,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>45729</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -6373,7 +6635,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6386,7 +6648,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>45729</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -6396,7 +6658,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6409,7 +6671,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>45729</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -6419,7 +6681,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6432,7 +6694,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>45729</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -6442,7 +6704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6455,7 +6717,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>45733</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -6465,7 +6727,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6478,7 +6740,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>45733</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -6488,7 +6750,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6501,7 +6763,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="4" t="n">
         <v>45734</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -6511,7 +6773,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6524,7 +6786,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="4" t="n">
         <v>45734</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -6534,7 +6796,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6547,7 +6809,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="4" t="n">
         <v>45734</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -6557,7 +6819,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6570,7 +6832,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="4" t="n">
         <v>45734</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -6580,7 +6842,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6593,7 +6855,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="4" t="n">
         <v>45735</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -6603,7 +6865,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6616,7 +6878,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="4" t="n">
         <v>45735</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -6626,7 +6888,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6639,7 +6901,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="4" t="n">
         <v>45735</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -6649,7 +6911,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6662,7 +6924,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="4" t="n">
         <v>45736</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -6672,7 +6934,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6685,7 +6947,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="4" t="n">
         <v>45738</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -6695,7 +6957,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6708,7 +6970,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="4" t="n">
         <v>45738</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -6718,7 +6980,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6731,7 +6993,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="4" t="n">
         <v>45738</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -6741,7 +7003,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6754,7 +7016,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="4" t="n">
         <v>45738</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -6764,7 +7026,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6777,7 +7039,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="4" t="n">
         <v>45738</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -6787,7 +7049,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6800,7 +7062,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="4" t="n">
         <v>45741</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -6810,7 +7072,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>618500</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6823,7 +7085,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="4" t="n">
         <v>45741</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -6833,7 +7095,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6846,7 +7108,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="4" t="n">
         <v>45741</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -6856,7 +7118,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6869,7 +7131,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="4" t="n">
         <v>45743</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -6879,7 +7141,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6892,7 +7154,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="4" t="n">
         <v>45743</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -6902,7 +7164,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6915,7 +7177,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="4" t="n">
         <v>45744</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -6925,7 +7187,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6938,7 +7200,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="4" t="n">
         <v>45745</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -6948,7 +7210,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7015,7 +7277,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45748</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -7025,7 +7287,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -7038,7 +7300,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45748</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -7048,7 +7310,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7061,7 +7323,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45750</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -7071,7 +7333,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7084,7 +7346,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45751</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -7094,7 +7356,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>623400</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7107,7 +7369,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45754</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -7117,7 +7379,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7130,7 +7392,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45754</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -7140,7 +7402,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7153,7 +7415,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45755</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -7163,7 +7425,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7176,7 +7438,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45759</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -7186,7 +7448,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7199,7 +7461,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45760</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -7209,7 +7471,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7222,7 +7484,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45760</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -7232,7 +7494,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7245,7 +7507,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45762</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -7255,7 +7517,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7268,7 +7530,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45764</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -7278,7 +7540,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7291,7 +7553,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45770</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -7301,7 +7563,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7314,7 +7576,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45770</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -7324,7 +7586,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7337,7 +7599,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45773</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -7347,7 +7609,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7360,7 +7622,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45774</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -7370,7 +7632,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7383,7 +7645,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45776</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -7393,7 +7655,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7406,7 +7668,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45777</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -7416,7 +7678,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7483,7 +7745,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45778</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -7493,7 +7755,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -7506,7 +7768,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45778</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -7516,7 +7778,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7529,7 +7791,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45778</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -7539,7 +7801,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7552,7 +7814,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45779</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -7562,7 +7824,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7575,7 +7837,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45779</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -7585,7 +7847,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7598,7 +7860,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45783</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -7608,7 +7870,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7621,7 +7883,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45784</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -7631,7 +7893,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7644,7 +7906,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45784</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -7654,7 +7916,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7667,7 +7929,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45784</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -7677,7 +7939,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7690,7 +7952,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45784</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -7700,7 +7962,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7713,7 +7975,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45785</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -7723,7 +7985,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7736,7 +7998,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45787</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -7746,7 +8008,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7759,7 +8021,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45787</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -7769,7 +8031,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7782,7 +8044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45788</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -7792,7 +8054,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7805,7 +8067,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45790</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -7815,7 +8077,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7828,7 +8090,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45791</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -7838,7 +8100,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7851,7 +8113,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45792</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -7861,7 +8123,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7874,7 +8136,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45793</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -7884,7 +8146,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>618500</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7897,7 +8159,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45793</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -7907,7 +8169,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7920,7 +8182,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45793</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -7930,7 +8192,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -7943,7 +8205,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45794</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -7953,7 +8215,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -7966,7 +8228,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45794</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -7976,7 +8238,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -7989,7 +8251,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45797</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -7999,7 +8261,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8012,7 +8274,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45797</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -8022,7 +8284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8035,7 +8297,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>45798</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -8045,7 +8307,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8058,7 +8320,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>45798</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -8068,7 +8330,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8081,7 +8343,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>45799</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -8091,7 +8353,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -8104,7 +8366,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>45801</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -8114,7 +8376,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -8127,7 +8389,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>45803</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -8137,7 +8399,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -8150,7 +8412,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>45804</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -8160,7 +8422,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -8173,7 +8435,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>45804</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -8183,7 +8445,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -8196,7 +8458,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="4" t="n">
         <v>45804</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -8206,7 +8468,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -8273,7 +8535,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45811</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -8283,7 +8545,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -8296,7 +8558,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45812</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -8306,7 +8568,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -8319,7 +8581,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45812</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -8329,7 +8591,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -8342,7 +8604,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45815</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -8352,7 +8614,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8365,7 +8627,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45815</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -8375,7 +8637,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8388,7 +8650,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45815</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -8398,7 +8660,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8411,7 +8673,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45819</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -8421,7 +8683,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8434,7 +8696,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45819</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -8444,7 +8706,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8457,7 +8719,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45820</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -8467,7 +8729,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8480,7 +8742,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45822</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -8490,7 +8752,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8503,7 +8765,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45822</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -8513,7 +8775,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8526,7 +8788,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45822</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -8536,7 +8798,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>580000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -8549,7 +8811,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45824</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -8559,7 +8821,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -8572,7 +8834,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45825</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -8582,7 +8844,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8595,7 +8857,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45827</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -8605,7 +8867,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8618,7 +8880,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45828</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -8628,7 +8890,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -8641,7 +8903,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45828</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -8651,7 +8913,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>455100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -8664,7 +8926,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45828</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -8674,7 +8936,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8687,7 +8949,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45829</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -8697,7 +8959,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8710,7 +8972,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45829</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -8720,7 +8982,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8733,7 +8995,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45833</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -8743,7 +9005,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8756,7 +9018,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45833</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -8766,7 +9028,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8779,7 +9041,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45835</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -8789,7 +9051,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8802,7 +9064,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45835</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -8812,7 +9074,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8825,7 +9087,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>45835</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -8835,7 +9097,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8848,7 +9110,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>45835</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -8858,7 +9120,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8871,7 +9133,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>45836</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -8881,7 +9143,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -8894,7 +9156,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>45836</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -8904,7 +9166,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>580000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -8917,7 +9179,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>45837</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -8927,7 +9189,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -8940,7 +9202,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>45837</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -8950,7 +9212,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -8963,7 +9225,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>45837</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -8973,7 +9235,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -8986,7 +9248,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="4" t="n">
         <v>45837</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -8996,7 +9258,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9009,7 +9271,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="4" t="n">
         <v>45838</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -9019,7 +9281,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -9086,7 +9348,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45839</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -9096,7 +9358,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -9109,7 +9371,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45839</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -9119,7 +9381,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>455100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -9132,7 +9394,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45841</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -9142,7 +9404,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -9155,7 +9417,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45841</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -9165,7 +9427,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -9178,7 +9440,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45842</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -9188,7 +9450,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9201,7 +9463,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45842</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -9211,7 +9473,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -9224,7 +9486,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45843</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -9234,7 +9496,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -9247,7 +9509,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45843</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -9257,7 +9519,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9270,7 +9532,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45845</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -9280,7 +9542,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>651000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9293,7 +9555,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45845</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -9303,7 +9565,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>627000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9316,7 +9578,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45846</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -9326,7 +9588,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9339,7 +9601,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45846</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -9349,7 +9611,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9362,7 +9624,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45847</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -9372,7 +9634,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9385,7 +9647,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45847</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -9395,7 +9657,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9408,7 +9670,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45847</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -9418,7 +9680,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9431,7 +9693,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45847</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -9441,7 +9703,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9454,7 +9716,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45848</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -9464,7 +9726,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -9477,7 +9739,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45848</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -9487,7 +9749,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>626100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -9500,7 +9762,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45852</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -9510,7 +9772,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -9523,7 +9785,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45853</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -9533,7 +9795,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -9546,7 +9808,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45856</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -9556,7 +9818,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -9569,7 +9831,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45857</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -9579,7 +9841,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>622600</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -9592,7 +9854,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45867</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -9602,7 +9864,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -9615,7 +9877,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45867</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -9625,7 +9887,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>616000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
